--- a/naver-place-crawler/results_derma/옹진군_피부과.xlsx
+++ b/naver-place-crawler/results_derma/옹진군_피부과.xlsx
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>본의원</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>예스피부과의원</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yesdermatology2022@naver.com</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>032-933-8765</t>
+          <t>032-752-9730</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 395 준프라자빌딩</t>
+          <t>인천광역시 중구 영종대로 184 4층 405호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://yesdermatology.com/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -597,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -608,22 +612,22 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>409</v>
+        <v>729</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>431</v>
       </c>
       <c r="R2" t="n">
-        <v>419</v>
+        <v>1160</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13070802</t>
+          <t>1602217880</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13070802</t>
+          <t>https://m.place.naver.com/place/1602217880</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -654,35 +658,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뷰티온의원 영종도점</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>본의원</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>guroclinic@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1370-7531</t>
+          <t>032-933-8765</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 중구 신도시남로142번길 6 메가스타영종 2층</t>
+          <t>인천광역시 강화군 강화읍 강화대로 395 준프라자빌딩</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://yeongjongdo.beautyon.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -698,22 +706,22 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>484</v>
+        <v>409</v>
       </c>
       <c r="Q3" t="n">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>588</v>
+        <v>419</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -722,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2001677341</t>
+          <t>13070802</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001677341</t>
+          <t>https://m.place.naver.com/place/13070802</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -744,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>예스피부과의원</t>
+          <t>영종센트럴피부과의원</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>yesdermatology2022@naver.com</t>
+          <t>centralderma@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>032-752-9730</t>
+          <t>0507-1435-2018</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로 184 4층 405호</t>
+          <t>인천광역시 중구 하늘중앙로 193 조양타워 3층, 309-313호 영종센트럴피부과</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://yesdermatology.com/</t>
+          <t>http://yjcentralskin.com/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -801,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>723</v>
+        <v>951</v>
       </c>
       <c r="Q4" t="n">
-        <v>425</v>
+        <v>379</v>
       </c>
       <c r="R4" t="n">
-        <v>1148</v>
+        <v>1330</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1602217880</t>
+          <t>1962468938</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1602217880</t>
+          <t>https://m.place.naver.com/place/1962468938</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -838,25 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에스오디21의원</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>리베리의원 영종도점</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>reberryclinicyj@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>032-751-9676</t>
+          <t>0507-1445-9095</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 14 3층 302호 SOD21의원</t>
+          <t>인천광역시 중구 하늘중앙로195번길 20 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://cafe.naver.com/sod21</t>
+          <t>https://yj.reberryclinic.com/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -871,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -887,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>86</v>
+        <v>1619</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>352</v>
       </c>
       <c r="R5" t="n">
-        <v>88</v>
+        <v>1971</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -906,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1892837233</t>
+          <t>1386437564</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1892837233</t>
+          <t>https://m.place.naver.com/place/1386437564</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -928,33 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>르네의원</t>
+          <t>에스오디21의원</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dallcyclei@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>webtick@gmail.com</t>
-        </is>
-      </c>
+          <t>lhh081409@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1354-5716</t>
+          <t>032-751-9676</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 21 3층 304-308호</t>
+          <t>인천광역시 중구 하늘중앙로195번길 14 3층 302호 SOD21의원</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.rene-clinic.com</t>
+          <t>http://cafe.naver.com/sod21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -964,7 +972,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -985,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1049</v>
+        <v>86</v>
       </c>
       <c r="Q6" t="n">
-        <v>461</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1510</v>
+        <v>89</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1862217079</t>
+          <t>1892837233</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862217079</t>
+          <t>https://m.place.naver.com/place/1892837233</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1026,29 +1034,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>해맑은의원</t>
+          <t>르네의원</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>asanhani@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>dallcyclei@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>webtick@gmail.com</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-751-6543</t>
+          <t>0507-1354-5716</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 중구 신도시남로 137 화평빌딩</t>
+          <t>인천광역시 중구 하늘중앙로195번길 21 3층 304-308호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.rene-clinic.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1063,7 +1075,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1079,17 +1091,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>465</v>
+        <v>1108</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>468</v>
       </c>
       <c r="R7" t="n">
-        <v>467</v>
+        <v>1576</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>13240738</t>
+          <t>1862217079</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240738</t>
+          <t>https://m.place.naver.com/place/1862217079</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1120,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>리베리의원 영종도점</t>
+          <t>아가파의원 영종도</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>reberryclinicyj@naver.com</t>
+          <t>k516tls@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1445-9095</t>
+          <t>032-746-1002</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 20 3층</t>
+          <t>인천광역시 중구 흰바위로 31 306호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://yj.reberryclinic.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1152,7 +1164,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1173,17 +1185,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1617</v>
+        <v>18</v>
       </c>
       <c r="Q8" t="n">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2024</v>
+        <v>18</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1386437564</t>
+          <t>1445959233</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1386437564</t>
+          <t>https://m.place.naver.com/place/1445959233</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1214,34 +1226,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>닥터스피부과의원 인천영종</t>
+          <t>해맑은의원</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>krh87@naver.com</t>
+          <t>asanhani@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>032-710-2346</t>
+          <t>032-751-6543</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로 197 조양타워2 4층</t>
+          <t>인천광역시 중구 신도시남로 137 화평빌딩</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://yeongjong.doctors365.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1262,22 +1274,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>299</v>
+        <v>466</v>
       </c>
       <c r="Q9" t="n">
-        <v>129</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2059209960</t>
+          <t>13240738</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2059209960</t>
+          <t>https://m.place.naver.com/place/13240738</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>영종센트럴피부과의원</t>
+          <t>닥터스피부과의원 인천영종</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>centralderma@naver.com</t>
+          <t>krh87@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1435-2018</t>
+          <t>032-710-2346</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로 193 조양타워 3층, 309-313호 영종센트럴피부과</t>
+          <t>인천광역시 중구 하늘중앙로 197 조양타워2 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://yjcentralskin.com/</t>
+          <t>https://yeongjong.doctors365.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1345,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1365,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>942</v>
+        <v>332</v>
       </c>
       <c r="Q10" t="n">
-        <v>365</v>
+        <v>143</v>
       </c>
       <c r="R10" t="n">
-        <v>1307</v>
+        <v>475</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1962468938</t>
+          <t>2059209960</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1962468938</t>
+          <t>https://m.place.naver.com/place/2059209960</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1402,35 +1414,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아가파의원 영종도</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>뷰티온의원 영종도점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>chaechae518@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>032-746-1002</t>
+          <t>0507-1370-7531</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 31 306호</t>
+          <t>인천광역시 중구 신도시남로142번길 6 메가스타영종 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://yeongjongdo.beautyon.co.kr/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1446,22 +1462,22 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>18</v>
+        <v>599</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="R11" t="n">
-        <v>18</v>
+        <v>698</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,17 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1445959233</t>
+          <t>2001677341</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1445959233</t>
+          <t>https://m.place.naver.com/place/2001677341</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1513,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kunnamu7582@naver.com</t>
+          <t>asggsa256@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1574,7 +1590,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1586,29 +1602,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>주내과의원</t>
+          <t>인하국제의원</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sidecar007@naver.com</t>
+          <t>inha_imc@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>032-751-7582</t>
+          <t>032-206-1888</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 31 에어로시티</t>
+          <t>인천광역시 중구 공항로424번길 84 인하국제의료센터</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.inhaim.com/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1618,7 +1634,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1643,13 +1659,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>140</v>
+        <v>8</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1658,17 +1674,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>13240739</t>
+          <t>38494761</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240739</t>
+          <t>https://m.place.naver.com/place/38494761</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1680,24 +1696,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>임성식내과의원</t>
+          <t>주내과의원</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ghssghss@naver.com</t>
+          <t>ipsi7717@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>032-932-3375</t>
+          <t>032-751-7582</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 395 3층</t>
+          <t>인천광역시 중구 흰바위로 31 에어로시티</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1737,13 +1753,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>362</v>
+        <v>140</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>363</v>
+        <v>141</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1752,17 +1768,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1587926050</t>
+          <t>13240739</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1587926050</t>
+          <t>https://m.place.naver.com/place/13240739</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1774,44 +1790,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>영종속시원내과의원</t>
+          <t>편안내과의원</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>imed0826@naver.com</t>
+          <t>kwonjuhee1@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1380-9576</t>
+          <t>0507-1478-2244</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로 197 조양타워2 5층 501호</t>
+          <t>인천광역시 중구 하늘별빛로 71</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://yjsswclinic.kr/</t>
+          <t>http://편안내과.com</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1831,13 +1847,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>202</v>
+        <v>377</v>
       </c>
       <c r="Q15" t="n">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>313</v>
+        <v>381</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1846,17 +1862,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1155107281</t>
+          <t>36655188</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155107281</t>
+          <t>https://m.place.naver.com/place/36655188</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1868,29 +1884,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>인하국제의원</t>
+          <t>영종속시원내과의원</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>inha_imc@naver.com</t>
+          <t>imed0826@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>032-206-1888</t>
+          <t>0507-1380-9576</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 중구 공항로424번길 84 인하국제의료센터</t>
+          <t>인천광역시 중구 하늘중앙로 197 조양타워2 5층 501호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://www.inhaim.com/</t>
+          <t>https://yjsswclinic.kr/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1925,13 +1941,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>8</v>
+        <v>207</v>
       </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="R16" t="n">
-        <v>16</v>
+        <v>323</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1940,17 +1956,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>38494761</t>
+          <t>1155107281</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38494761</t>
+          <t>https://m.place.naver.com/place/1155107281</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1962,30 +1978,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>편안내과의원</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>임성식내과의원</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ghssghss@naver.com</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1478-2244</t>
+          <t>032-932-3375</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로 71</t>
+          <t>인천광역시 강화군 강화읍 강화대로 395 3층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://편안내과.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1995,7 +2015,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2015,13 +2035,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2030,17 +2050,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>36655188</t>
+          <t>1587926050</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36655188</t>
+          <t>https://m.place.naver.com/place/1587926050</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2052,34 +2072,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>연세공항의원</t>
+          <t>정 의원</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>behappy_dec@naver.com</t>
+          <t>42w9opfa@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>032-751-6119</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 중구 공항로424번길 66 지하 1층</t>
+          <t>인천광역시 강화군 강화읍 강화대로 395</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://연세공항의원.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2089,7 +2105,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2105,17 +2121,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>403</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>410</v>
+        <v>2</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2124,17 +2140,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13240727</t>
+          <t>1704510554</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240727</t>
+          <t>https://m.place.naver.com/place/1704510554</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2146,20 +2162,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>정 의원</t>
+          <t>인천국제공항의원 제1터미널</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>42w9opfa@naver.com</t>
+          <t>inhaamc@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>032-743-3119</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 395</t>
+          <t>인천광역시 중구 공항로 271 인천공항 제1터미널 지하1층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2199,13 +2219,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>351</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>497</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2214,17 +2234,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1704510554</t>
+          <t>21560045</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1704510554</t>
+          <t>https://m.place.naver.com/place/21560045</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2236,44 +2256,44 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>엠케이의원</t>
+          <t>연세공항의원</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mkdental_@naver.com</t>
+          <t>aquacola227@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1400-5162</t>
+          <t>032-751-6119</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종해안남로321번길 186 파라다이스시티 H201</t>
+          <t>인천광역시 중구 공항로424번길 66 지하 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mkclinic_kr</t>
+          <t>http://연세공항의원.com/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2293,13 +2313,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>402</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>409</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2308,17 +2328,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1460899072</t>
+          <t>13240727</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1460899072</t>
+          <t>https://m.place.naver.com/place/13240727</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2330,29 +2350,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>비앤씨의원</t>
+          <t>길상의원</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>bncclinic@naver.com</t>
+          <t>bsing975@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1467-8836</t>
+          <t>032-937-5105</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 3 영종M타워 4, 5, 6층</t>
+          <t>인천광역시 강화군 길상면 온수길 23 2층 길상의원</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://bncclinic.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2362,7 +2382,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2387,13 +2407,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>544</v>
+        <v>166</v>
       </c>
       <c r="Q21" t="n">
-        <v>449</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>993</v>
+        <v>168</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2402,17 +2422,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1588439521</t>
+          <t>13241476</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1588439521</t>
+          <t>https://m.place.naver.com/place/13241476</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2424,25 +2444,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>영종삼성의원</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>비앤씨의원</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>bncclinic@naver.com</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>032-752-8275</t>
+          <t>0507-1467-8836</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로 100 신성하우스빌 5층 영종삼성의원</t>
+          <t>인천광역시 중구 하늘중앙로225번길 3 영종M타워 4, 5, 6층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://bncclinic.kr</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2452,7 +2476,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2477,13 +2501,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>135</v>
+        <v>544</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>450</v>
       </c>
       <c r="R22" t="n">
-        <v>137</v>
+        <v>994</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2492,17 +2516,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>12827055</t>
+          <t>1588439521</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12827055</t>
+          <t>https://m.place.naver.com/place/1588439521</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2514,29 +2538,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>인천국제공항의원 제1터미널</t>
+          <t>로하스의원</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>inhaamc@naver.com</t>
+          <t>wife1978@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>032-743-3119</t>
+          <t>0507-1312-6977</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 중구 공항로 271 인천공항 제1터미널 지하1층</t>
+          <t>인천광역시 중구 하늘달빛로 94 스타타워 5층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/inhaamc</t>
+          <t>http://www.365lohas.co.kr</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2551,7 +2575,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2562,7 +2586,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2571,13 +2595,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>351</v>
+        <v>598</v>
       </c>
       <c r="Q23" t="n">
-        <v>146</v>
+        <v>902</v>
       </c>
       <c r="R23" t="n">
-        <v>497</v>
+        <v>1500</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2586,17 +2610,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>21560045</t>
+          <t>1119171326</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21560045</t>
+          <t>https://m.place.naver.com/place/1119171326</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2608,20 +2632,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>길상의원</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>하늘메디컬의원 건강검진센터</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>seowon0506@naver.com</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>032-937-5105</t>
+          <t>032-752-6008</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 길상면 온수길 23 2층 길상의원</t>
+          <t>인천광역시 중구 하늘중앙로 193 조양타워4층, 401호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2661,13 +2689,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>166</v>
+        <v>354</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>168</v>
+        <v>361</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2676,17 +2704,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>13241476</t>
+          <t>37089382</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241476</t>
+          <t>https://m.place.naver.com/place/37089382</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2698,29 +2726,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>로하스의원</t>
+          <t>성모연합의원</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>wife1978@naver.com</t>
+          <t>wacoh1bu@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1312-6977</t>
+          <t>041-352-8275</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 94 스타타워 5층</t>
+          <t>충청남도 당진시 석문면 석문방조제로 2210 성모연합의원</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://www.365lohas.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2730,7 +2758,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2746,7 +2774,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2755,13 +2783,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>588</v>
+        <v>41</v>
       </c>
       <c r="Q25" t="n">
-        <v>893</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1481</v>
+        <v>41</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2770,17 +2798,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1119171326</t>
+          <t>11541633</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1119171326</t>
+          <t>https://m.place.naver.com/place/11541633</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2792,29 +2820,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>성모연합의원</t>
+          <t>엠케이의원</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>wacoh1bu@naver.com</t>
+          <t>mkdental_@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>041-352-8275</t>
+          <t>0507-1400-5162</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>충청남도 당진시 석문면 석문방조제로 2210 성모연합의원</t>
+          <t>인천광역시 중구 영종해안남로321번길 186 파라다이스시티 H201</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mkclinic_kr</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2824,7 +2852,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2845,17 +2873,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2864,17 +2892,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>11541633</t>
+          <t>1460899072</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11541633</t>
+          <t>https://m.place.naver.com/place/1460899072</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2886,20 +2914,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>하늘메디컬의원 건강검진센터</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>영종삼성의원</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>chung5ju@naver.com</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>032-752-6008</t>
+          <t>032-752-8275</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로 193 조양타워4층, 401호</t>
+          <t>인천광역시 중구 영종대로 100 신성하우스빌 5층 영종삼성의원</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2939,13 +2971,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>354</v>
+        <v>135</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>361</v>
+        <v>137</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2954,17 +2986,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>37089382</t>
+          <t>12827055</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37089382</t>
+          <t>https://m.place.naver.com/place/12827055</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2976,20 +3008,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>대호지면보건지소</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>주문보건지소</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>cjwoni30@naver.com</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>041-360-6190</t>
+          <t>032-932-7008</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>충청남도 당진시 대호지면 4.4만세로 55-1</t>
+          <t>인천광역시 강화군 서도면 주문도1길 16-1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3032,10 +3068,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3044,17 +3080,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>21559932</t>
+          <t>19522409</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21559932</t>
+          <t>https://m.place.naver.com/place/19522409</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3066,24 +3102,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>주문보건지소</t>
+          <t>대호지면보건지소</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>smbakery@naver.com</t>
+          <t>dangjin2030@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>032-932-7008</t>
+          <t>041-360-6190</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 서도면 주문도1길 16-1</t>
+          <t>충청남도 당진시 대호지면 4.4만세로 55-1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3126,10 +3162,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3138,17 +3174,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>19522409</t>
+          <t>21559932</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19522409</t>
+          <t>https://m.place.naver.com/place/21559932</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3278,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3311,13 +3347,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q31" t="n">
         <v>13</v>
       </c>
       <c r="R31" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3336,7 +3372,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3466,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3483,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>pcparts@naver.com</t>
+          <t>dhrudgk115@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3528,7 +3564,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3540,30 +3576,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>키클소아청소년과의원</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>예스삼성소아청소년과의원</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>yessamsungped@naver.com</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>032-713-7950</t>
+          <t>0507-1353-9722</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 8-11 401호</t>
+          <t>인천광역시 중구 영종대로 184 예스타워17 4층 401호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/keekleped</t>
+          <t>https://link.inpock.co.kr/yessamsungped</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3573,7 +3613,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3593,13 +3633,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>958</v>
+        <v>245</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="R34" t="n">
-        <v>968</v>
+        <v>352</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3608,17 +3648,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1222173341</t>
+          <t>1871678192</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222173341</t>
+          <t>https://m.place.naver.com/place/1871678192</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3630,44 +3670,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>예스삼성소아청소년과의원</t>
+          <t>키클소아청소년과의원</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>yessamsungped@naver.com</t>
+          <t>mineat_@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1353-9722</t>
+          <t>032-713-7950</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로 184 예스타워17 4층 401호</t>
+          <t>인천광역시 중구 하늘별빛로65번길 8-11 401호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/yessamsungped</t>
+          <t>http://www.instagram.com/keekleped</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3687,13 +3727,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>245</v>
+        <v>958</v>
       </c>
       <c r="Q35" t="n">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="R35" t="n">
-        <v>351</v>
+        <v>968</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3702,17 +3742,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1871678192</t>
+          <t>1222173341</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1871678192</t>
+          <t>https://m.place.naver.com/place/1222173341</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3767,11 @@
           <t>인성의원</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>insunghani@naver.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
@@ -3802,7 +3846,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3874,10 +3918,10 @@
         <v>10</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3896,7 +3940,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3955,11 @@
           <t>베스트이비인후과의원</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>bestent59@naver.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
@@ -3986,7 +4034,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4059,13 +4107,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Q39" t="n">
         <v>8</v>
       </c>
       <c r="R39" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4084,7 +4132,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4226,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4247,13 +4295,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q41" t="n">
         <v>143</v>
       </c>
       <c r="R41" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4272,7 +4320,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4284,24 +4332,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>우리한의원</t>
+          <t>길상한의원</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1firstdoctor@naver.com</t>
+          <t>bsing975@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>032-932-9330</t>
+          <t>032-937-8565</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 416</t>
+          <t>인천광역시 강화군 길상면 마니산로 53</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4341,13 +4389,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>170</v>
+        <v>67</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>174</v>
+        <v>67</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4356,17 +4404,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>36332213</t>
+          <t>13116068</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36332213</t>
+          <t>https://m.place.naver.com/place/13116068</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4378,29 +4426,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>연한의원 백령</t>
+          <t>자성한의원</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>yeonhani7582@naver.com</t>
+          <t>jasungkmd@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>032-836-7582</t>
+          <t>032-719-8880</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 옹진군 백령면 백령로280번길 4-1 1층</t>
+          <t>인천광역시 강화군 강화읍 중앙로 68 2층 자성한의원</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jasungkmd</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4410,12 +4458,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4435,13 +4483,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4450,17 +4498,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1952008587</t>
+          <t>1228477451</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1952008587</t>
+          <t>https://m.place.naver.com/place/1228477451</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4472,25 +4520,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>운서한의원</t>
+          <t>강화한의원</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>portair@naver.com</t>
+          <t>khomsin@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>032-934-6336</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 236 307호 운서한의원</t>
+          <t>인천광역시 강화군 강화읍 강화대로393번길 5</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/khomsin</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4500,12 +4552,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4525,13 +4577,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>198</v>
+        <v>36</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4540,17 +4592,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>11673844</t>
+          <t>13241468</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11673844</t>
+          <t>https://m.place.naver.com/place/13241468</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4562,29 +4614,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>경희백향한의원</t>
+          <t>제일한의원</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>avalon234@naver.com</t>
+          <t>hwahwa312@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>032-932-1029</t>
+          <t>032-933-0087</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로404번길 4</t>
+          <t>인천광역시 강화군 강화읍 남문로 75</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://blog.daum.net/chance-4u</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4594,7 +4646,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4619,13 +4671,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4634,17 +4686,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>19531496</t>
+          <t>20713404</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19531496</t>
+          <t>https://m.place.naver.com/place/20713404</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4656,29 +4708,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>강화부부한의원</t>
+          <t>월곶한의원</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ganghwabubu@naver.com</t>
+          <t>o2clinic7711@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>032-934-5533</t>
+          <t>0507-1362-8471</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 향나무길 22</t>
+          <t>경기도 김포시 월곶면 애기봉로7번길 20-12 2층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ganghwabubu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4688,12 +4740,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4709,17 +4761,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R46" t="n">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4728,17 +4780,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>13241465</t>
+          <t>13142662</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241465</t>
+          <t>https://m.place.naver.com/place/13142662</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4750,25 +4802,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>청송한의원</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>경희백향한의원</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>avalon234@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>032-752-2228</t>
+          <t>032-932-1029</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 중구 운중로 22 중앙빌딩 2층</t>
+          <t>인천광역시 강화군 강화읍 강화대로404번길 4</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://blog.daum.net/chance-4u</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4778,7 +4834,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4803,13 +4859,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>145</v>
+        <v>23</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4818,17 +4874,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13240742</t>
+          <t>19531496</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240742</t>
+          <t>https://m.place.naver.com/place/19531496</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4840,29 +4896,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>도앤다한의원 하늘도시점</t>
+          <t>더조은경희한의원</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>lj456456@naver.com</t>
+          <t>kkslmjlove@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1340-8365</t>
+          <t>0507-1308-8276</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 8-13 금산빌딩 3층</t>
+          <t>인천광역시 강화군 강화읍 충렬사로 25 3층 303호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.doandda.com/home</t>
+          <t>https://blog.naver.com/kkslmjlove</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4877,7 +4933,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4897,13 +4953,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1406</v>
+        <v>153</v>
       </c>
       <c r="Q48" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="R48" t="n">
-        <v>1437</v>
+        <v>204</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4912,17 +4968,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1824737738</t>
+          <t>1964704753</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824737738</t>
+          <t>https://m.place.naver.com/place/1964704753</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4934,29 +4990,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>압구정미한의원</t>
+          <t>행림한의원</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>omdmin@naver.com</t>
+          <t>haengrim00@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>032-747-0112</t>
+          <t>032-747-1075</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 94 스타타워1 304호</t>
+          <t>인천광역시 중구 흰바위로 31 에어로시티 301</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/omdmin</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4966,12 +5022,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4991,13 +5047,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>33</v>
+        <v>193</v>
       </c>
       <c r="Q49" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="R49" t="n">
-        <v>76</v>
+        <v>195</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5006,17 +5062,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1878608600</t>
+          <t>11630173</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1878608600</t>
+          <t>https://m.place.naver.com/place/11630173</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5028,29 +5084,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>자성한의원</t>
+          <t>경희새벽한의원</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jasungkmd@naver.com</t>
+          <t>bottlejean@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>032-719-8880</t>
+          <t>032-932-7582</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 중앙로 68 2층 자성한의원</t>
+          <t>인천광역시 강화군 강화읍 중앙로 23 (일석빌딩) 1층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jasungkmd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5060,12 +5116,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5085,13 +5141,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5100,17 +5156,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1228477451</t>
+          <t>21062931</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228477451</t>
+          <t>https://m.place.naver.com/place/21062931</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5122,20 +5178,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>길상한의원</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>연한의원 백령</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>yeonhani7582@naver.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>032-937-8565</t>
+          <t>032-836-7582</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 길상면 마니산로 53</t>
+          <t>인천광역시 옹진군 백령면 백령로280번길 4-1 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5175,13 +5235,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5190,17 +5250,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>13116068</t>
+          <t>1952008587</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13116068</t>
+          <t>https://m.place.naver.com/place/1952008587</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5212,24 +5272,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>제일한의원</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>zcijbw4165@naver.com</t>
-        </is>
-      </c>
+          <t>운서한의원</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>032-933-0087</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 남문로 75</t>
+          <t>인천광역시 중구 흰바위로 236 307호 운서한의원</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5269,13 +5321,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>63</v>
+        <v>198</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5284,17 +5336,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>20713404</t>
+          <t>11673844</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20713404</t>
+          <t>https://m.place.naver.com/place/11673844</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5306,20 +5358,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>미소한의원</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>명인한의원</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>brightin5234@naver.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>032-752-2008</t>
+          <t>032-934-5805</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 중구 신도시남로 137 화평빌딩</t>
+          <t>인천광역시 강화군 강화읍 강화대로 375</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5359,13 +5415,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>329</v>
+        <v>56</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>334</v>
+        <v>56</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5374,17 +5430,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>13240741</t>
+          <t>19518812</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240741</t>
+          <t>https://m.place.naver.com/place/19518812</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5396,29 +5452,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>하늘튼튼한의원</t>
+          <t>압구정미한의원</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>tlsqkrgk@naver.com</t>
+          <t>omdmin@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>032-751-8875</t>
+          <t>032-747-0112</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 47 스타타워2 5층 504호 505호</t>
+          <t>인천광역시 중구 하늘달빛로 94 스타타워1 304호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://www.하늘튼튼한의원.com</t>
+          <t>https://blog.naver.com/omdmin</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5433,7 +5489,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5453,13 +5509,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>471</v>
+        <v>33</v>
       </c>
       <c r="Q54" t="n">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="R54" t="n">
-        <v>587</v>
+        <v>78</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5468,17 +5524,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1058870904</t>
+          <t>1878608600</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058870904</t>
+          <t>https://m.place.naver.com/place/1878608600</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5490,24 +5546,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>용정한의원</t>
+          <t>성심한의원</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mintchoco_s@naver.com</t>
+          <t>sungsimvv@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>032-933-4048</t>
+          <t>032-937-8122</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 갑룡길 118</t>
+          <t>인천광역시 강화군 길상면 강화동로 9</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5547,13 +5603,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5562,17 +5618,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>32473020</t>
+          <t>33586681</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32473020</t>
+          <t>https://m.place.naver.com/place/33586681</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5584,24 +5640,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>하늘부부한의원</t>
+          <t>장수한의원</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>idyoontk@naver.com</t>
+          <t>rhdwlseks@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>032-713-8675</t>
+          <t>041-666-1075</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로 193 조양타워 307호~308호</t>
+          <t>충청남도 서산시 대산읍 구진로 60-1</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5641,13 +5697,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>530</v>
+        <v>7</v>
       </c>
       <c r="Q56" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>683</v>
+        <v>7</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5656,17 +5712,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1535527854</t>
+          <t>1404983569</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1535527854</t>
+          <t>https://m.place.naver.com/place/1404983569</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5678,29 +5734,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>월곶한의원</t>
+          <t>강화부부한의원</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>o2clinic7711@naver.com</t>
+          <t>ganghwabubu@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1362-8471</t>
+          <t>032-934-5533</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 김포시 월곶면 애기봉로7번길 20-12 2층</t>
+          <t>인천광역시 강화군 강화읍 향나무길 22</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ganghwabubu</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5710,12 +5766,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5731,17 +5787,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R57" t="n">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5750,17 +5806,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13142662</t>
+          <t>13241465</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13142662</t>
+          <t>https://m.place.naver.com/place/13241465</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5772,34 +5828,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>영종모래내한의원 인천운서</t>
+          <t>영종한의원</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>yjmoranae@naver.com</t>
+          <t>itpptlt12@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>032-724-9947</t>
+          <t>0507-1412-1276</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 51 영종 롯데마트 3층</t>
+          <t>인천광역시 중구 하늘달빛로 94 403호 영종한의원</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yjmoranae</t>
+          <t>http://pf.kakao.com/_XrxoDn</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5809,7 +5865,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5820,7 +5876,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5829,13 +5885,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>998</v>
+        <v>583</v>
       </c>
       <c r="Q58" t="n">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="R58" t="n">
-        <v>1420</v>
+        <v>675</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5844,17 +5900,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1233128399</t>
+          <t>642061257</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1233128399</t>
+          <t>https://m.place.naver.com/place/642061257</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5866,29 +5922,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>하늘경희한의원</t>
+          <t>영종모래내한의원 인천운서</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>omd_kdj@naver.com</t>
+          <t>yjmoranae@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1483-1091</t>
+          <t>032-724-9947</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로 75 4층 402호</t>
+          <t>인천광역시 중구 흰바위로 51 영종 롯데마트 3층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/omd_kdj</t>
+          <t>https://blog.naver.com/yjmoranae</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5923,13 +5979,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>90</v>
+        <v>1013</v>
       </c>
       <c r="Q59" t="n">
-        <v>7</v>
+        <v>497</v>
       </c>
       <c r="R59" t="n">
-        <v>97</v>
+        <v>1510</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5938,17 +5994,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1402312673</t>
+          <t>1233128399</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1402312673</t>
+          <t>https://m.place.naver.com/place/1233128399</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5960,25 +6016,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>감초한의원</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>하늘경희한의원</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>omd_kdj@naver.com</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>032-934-2163</t>
+          <t>0507-1483-1091</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 청하동길9번길 7</t>
+          <t>인천광역시 중구 하늘별빛로 75 4층 402호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/omd_kdj</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5988,12 +6048,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6013,13 +6073,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R60" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6028,17 +6088,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>13241455</t>
+          <t>1402312673</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241455</t>
+          <t>https://m.place.naver.com/place/1402312673</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6050,39 +6110,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>영종한의원</t>
+          <t>채준환한의원</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>itpptlt12@naver.com</t>
+          <t>mrhanbit@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1412-1276</t>
+          <t>032-937-7574</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 94 403호 영종한의원</t>
+          <t>인천광역시 강화군 화도면 마니산로 716</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XrxoDn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6098,7 +6158,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6107,13 +6167,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>565</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>657</v>
+        <v>1</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6122,17 +6182,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>642061257</t>
+          <t>1808971613</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/642061257</t>
+          <t>https://m.place.naver.com/place/1808971613</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6144,25 +6204,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>늘곁한의원</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>석문한의원</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>nayaeh@naver.com</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>032-716-5975</t>
+          <t>041-356-7510</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 334 1층</t>
+          <t>충청남도 당진시 석문면 대호로 1581 석문한의원</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/alwayswithyou_kmed/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6172,7 +6236,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6193,17 +6257,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="Q62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6212,17 +6276,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1610115216</t>
+          <t>19531471</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1610115216</t>
+          <t>https://m.place.naver.com/place/19531471</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6234,24 +6298,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>성심한의원</t>
+          <t>미소한의원</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sungsimvv@naver.com</t>
+          <t>drlung@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>032-937-8122</t>
+          <t>032-752-2008</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 길상면 강화동로 9</t>
+          <t>인천광역시 중구 신도시남로 137 화평빌딩</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6291,13 +6355,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R63" t="n">
-        <v>96</v>
+        <v>334</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6306,17 +6370,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>33586681</t>
+          <t>13240741</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33586681</t>
+          <t>https://m.place.naver.com/place/13240741</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6328,29 +6392,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>경희새벽한의원</t>
+          <t>도앤다한의원 하늘도시점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>bottlejean@naver.com</t>
+          <t>lj456456@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>032-932-7582</t>
+          <t>0507-1340-8365</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 중앙로 23 (일석빌딩) 1층</t>
+          <t>인천광역시 중구 하늘별빛로65번길 8-13 금산빌딩 3층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.doandda.com/home</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6360,7 +6424,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6385,13 +6449,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>64</v>
+        <v>1407</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R64" t="n">
-        <v>64</v>
+        <v>1438</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6400,17 +6464,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>21062931</t>
+          <t>1824737738</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21062931</t>
+          <t>https://m.place.naver.com/place/1824737738</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6422,24 +6486,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>석문한의원</t>
+          <t>하늘부부한의원</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>dasolbb@naver.com</t>
+          <t>idyoontk@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>041-356-7510</t>
+          <t>032-713-8675</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>충청남도 당진시 석문면 대호로 1581 석문한의원</t>
+          <t>인천광역시 중구 하늘중앙로 193 조양타워 307호~308호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6479,13 +6543,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>10</v>
+        <v>534</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="R65" t="n">
-        <v>10</v>
+        <v>689</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6494,17 +6558,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>19531471</t>
+          <t>1535527854</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19531471</t>
+          <t>https://m.place.naver.com/place/1535527854</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6516,20 +6580,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>채준환한의원</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>감초한의원</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ohchang67@naver.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>032-937-7574</t>
+          <t>032-934-2163</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 화도면 마니산로 716</t>
+          <t>인천광역시 강화군 강화읍 청하동길9번길 7</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6569,13 +6637,13 @@
         </is>
       </c>
       <c r="P66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>1</v>
-      </c>
       <c r="R66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6584,17 +6652,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1808971613</t>
+          <t>13241455</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1808971613</t>
+          <t>https://m.place.naver.com/place/13241455</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6606,29 +6674,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>더조은경희한의원</t>
+          <t>하늘튼튼한의원</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kkslmjlove@naver.com</t>
+          <t>tlsqkrgk@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1308-8276</t>
+          <t>032-751-8875</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 충렬사로 25 3층 303호</t>
+          <t>인천광역시 중구 자연대로 47 스타타워2 5층 504호 505호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kkslmjlove</t>
+          <t>http://www.하늘튼튼한의원.com</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6643,7 +6711,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6663,13 +6731,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>152</v>
+        <v>467</v>
       </c>
       <c r="Q67" t="n">
-        <v>51</v>
+        <v>160</v>
       </c>
       <c r="R67" t="n">
-        <v>203</v>
+        <v>627</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6678,17 +6746,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1964704753</t>
+          <t>1058870904</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1964704753</t>
+          <t>https://m.place.naver.com/place/1058870904</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6700,24 +6768,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>명인한의원</t>
+          <t>청송한의원</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>brightin5234@naver.com</t>
+          <t>safetystt667@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>032-934-5805</t>
+          <t>032-752-2228</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 375</t>
+          <t>인천광역시 중구 운중로 22 중앙빌딩 2층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6757,13 +6825,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R68" t="n">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6772,17 +6840,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>19518812</t>
+          <t>13240742</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19518812</t>
+          <t>https://m.place.naver.com/place/13240742</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6794,24 +6862,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>장수한의원</t>
+          <t>우리한의원</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>rhdwlseks@naver.com</t>
+          <t>1firstdoctor@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>041-666-1075</t>
+          <t>032-932-9330</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>충청남도 서산시 대산읍 구진로 60-1</t>
+          <t>인천광역시 강화군 강화읍 강화대로 416</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6851,13 +6919,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>7</v>
+        <v>170</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R69" t="n">
-        <v>7</v>
+        <v>174</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6866,17 +6934,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1404983569</t>
+          <t>36332213</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404983569</t>
+          <t>https://m.place.naver.com/place/36332213</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6888,29 +6956,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>강화한의원</t>
+          <t>용정한의원</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>khomsin@naver.com</t>
+          <t>mintchoco_s@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>032-934-6336</t>
+          <t>032-933-4048</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로393번길 5</t>
+          <t>인천광역시 강화군 강화읍 갑룡길 118</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/khomsin</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6920,12 +6988,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6945,13 +7013,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>36</v>
+        <v>158</v>
       </c>
       <c r="Q70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6960,17 +7028,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>13241468</t>
+          <t>32473020</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241468</t>
+          <t>https://m.place.naver.com/place/32473020</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6982,29 +7050,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>행림한의원</t>
+          <t>늘곁한의원</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>haengrim00@naver.com</t>
+          <t>cheolsoo58@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>032-747-1075</t>
+          <t>032-716-5975</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 31 에어로시티 301</t>
+          <t>인천광역시 강화군 강화읍 강화대로 334 1층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/alwayswithyou_kmed/</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7014,7 +7082,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7035,17 +7103,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="Q71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R71" t="n">
-        <v>195</v>
+        <v>87</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7054,17 +7122,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>11630173</t>
+          <t>1610115216</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11630173</t>
+          <t>https://m.place.naver.com/place/1610115216</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
